--- a/data/trans_dic/IP16B_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP16B_2023-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores vacunados de la triple vírica</t>
+          <t>Menores vacunados de la triple vírica (tasa de respuesta: 98,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>93,94; 100,0</t>
+          <t>94,82; 100,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>91,18; 99,34</t>
+          <t>92,39; 99,36</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>94,69; 99,47</t>
+          <t>94,94; 99,37</t>
         </is>
       </c>
     </row>
@@ -621,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>97,95; 99,5</t>
+          <t>97,95; 99,49</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>97,11; 98,88</t>
+          <t>96,96; 98,89</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>97,77; 99,0</t>
+          <t>97,69; 99,01</t>
         </is>
       </c>
     </row>
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>93,33; 98,45</t>
+          <t>93,64; 98,5</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>97,34; 99,6</t>
+          <t>97,17; 99,54</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>96,2; 98,79</t>
+          <t>96,26; 98,78</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>97,44; 99,03</t>
+          <t>97,54; 99,06</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>97,3; 98,86</t>
+          <t>97,35; 98,84</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>97,72; 98,82</t>
+          <t>97,68; 98,79</t>
         </is>
       </c>
     </row>
@@ -752,4 +753,380 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores vacunados de la triple vírica (tasa de respuesta: 98,91%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>53630</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>59301</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>112931</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>51426; 54233</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>56397; 60651</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>109445; 114546</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>627</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>631</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1258</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>449997</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>497939</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>947937</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>445602; 452570</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>491927; 501751</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>940090; 952704</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>219</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>451</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>142609</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>179941</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>322551</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>138096; 145257</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>177023; 181336</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>317321; 325632</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>913</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>941</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1854</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>646237</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>737181</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1383417</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>640485; 650457</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>730668; 741879</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>1374596; 1390230</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP16B_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP16B_2023-Estudios-trans_dic.xlsx
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>94,82; 100,0</t>
+          <t>94,19; 100,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>92,39; 99,36</t>
+          <t>91,71; 99,36</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>94,94; 99,37</t>
+          <t>94,87; 99,48</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>97,95; 99,49</t>
+          <t>97,99; 99,5</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>96,96; 98,89</t>
+          <t>97,03; 98,88</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>97,69; 99,01</t>
+          <t>97,66; 99,04</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>93,64; 98,5</t>
+          <t>93,47; 98,57</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>97,17; 99,54</t>
+          <t>97,01; 99,56</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>96,26; 98,78</t>
+          <t>96,36; 98,88</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>97,54; 99,06</t>
+          <t>97,54; 99,08</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>97,35; 98,84</t>
+          <t>97,28; 98,82</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>97,68; 98,79</t>
+          <t>97,76; 98,78</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>51426; 54233</t>
+          <t>51083; 54233</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>56397; 60651</t>
+          <t>55982; 60654</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>109445; 114546</t>
+          <t>109361; 114682</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>445602; 452570</t>
+          <t>445754; 452648</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>491927; 501751</t>
+          <t>492282; 501668</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>940090; 952704</t>
+          <t>939729; 953030</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>138096; 145257</t>
+          <t>137849; 145362</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>177023; 181336</t>
+          <t>176735; 181372</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>317321; 325632</t>
+          <t>317650; 325943</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>640485; 650457</t>
+          <t>640480; 650547</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>730668; 741879</t>
+          <t>730188; 741701</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1374596; 1390230</t>
+          <t>1375671; 1389967</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP16B_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP16B_2023-Estudios-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,9%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>94,19; 100,0</t>
+          <t>90,7; 99,45</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>91,71; 99,36</t>
+          <t>93,85; 100,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>94,87; 99,48</t>
+          <t>94,5; 99,42</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,63%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>97,99; 99,5</t>
+          <t>97,17; 98,98</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>97,03; 98,88</t>
+          <t>98,23; 99,57</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>97,66; 99,04</t>
+          <t>97,89; 99,08</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,9%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>93,47; 98,57</t>
+          <t>97,65; 99,66</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>97,01; 99,56</t>
+          <t>93,26; 98,47</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>96,36; 98,88</t>
+          <t>96,22; 98,84</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,4%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>97,54; 99,08</t>
+          <t>97,42; 98,93</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>97,28; 98,82</t>
+          <t>97,51; 99,07</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>97,76; 98,78</t>
+          <t>97,81; 98,88</t>
         </is>
       </c>
     </row>
@@ -780,12 +780,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -833,12 +833,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>67</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>53630</t>
+          <t>54303</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>59301</t>
+          <t>45874</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>112931</t>
+          <t>100177</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>51083; 54233</t>
+          <t>50720; 55612</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>55982; 60654</t>
+          <t>43544; 46399</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>109361; 114682</t>
+          <t>96698; 101731</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>631</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>627</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>631</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>449997</t>
+          <t>458588</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>497939</t>
+          <t>422992</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>947937</t>
+          <t>881580</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>445754; 452648</t>
+          <t>453600; 462009</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>492282; 501668</t>
+          <t>419450; 425158</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>939729; 953030</t>
+          <t>874907; 885538</t>
         </is>
       </c>
     </row>
@@ -979,12 +979,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>219</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>232</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>142609</t>
+          <t>166077</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>179941</t>
+          <t>143056</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>322551</t>
+          <t>309133</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>137849; 145362</t>
+          <t>163927; 167293</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>176735; 181372</t>
+          <t>137916; 145622</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>317650; 325943</t>
+          <t>303827; 312090</t>
         </is>
       </c>
     </row>
@@ -1052,12 +1052,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>941</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>913</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>941</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>646237</t>
+          <t>678968</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>737181</t>
+          <t>611922</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1383417</t>
+          <t>1290890</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>640480; 650547</t>
+          <t>672766; 683176</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>730188; 741701</t>
+          <t>605820; 615501</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1375671; 1389967</t>
+          <t>1283099; 1297147</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP16B_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP16B_2023-Estudios-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,290 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores vacunados de la triple vírica (tasa de respuesta: 98,91%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>Primarios</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>97,1%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>98,87%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>97,9%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>90,7; 99,45</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>93,85; 100,0</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>94,5; 99,42</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>Secundarios</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>98,24%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>99,06%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>98,63%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>97,17; 98,98</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>98,23; 99,57</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>97,89; 99,08</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>98,93%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>96,74%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>97,9%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>97,65; 99,66</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>93,26; 98,47</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>96,22; 98,84</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>98,32%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>98,49%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>98,4%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>97,42; 98,93</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>97,51; 99,07</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>97,81; 98,88</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -828,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.9710459499320601</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.9886902407797412</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.9790469988234608</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>54303</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>45874</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>100177</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.9069701330340436</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.938478997019194</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.9450433609550918</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>50720; 55612</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>43544; 46399</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>96698; 101731</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.9944506133895633</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.994231682189273</v>
       </c>
     </row>
     <row r="7">
@@ -901,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>631</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>627</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1258</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.9824315572137068</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.990590076788148</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.9863292701569467</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>458588</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>422992</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>881580</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.9717451400259153</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.982295364929997</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.9788632195258311</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>453600; 462009</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>419450; 425158</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>874907; 885538</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.9897603849474623</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.9956626071263051</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.9907577818234041</v>
       </c>
     </row>
     <row r="10">
@@ -974,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>219</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>451</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.9893220916096711</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.9673812981191204</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.979046213738035</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>166077</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>143056</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>309133</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.9765174977475537</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.9326190036624467</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.9622425432696494</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>163927; 167293</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>137916; 145622</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>303827; 312090</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.996570137144168</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.9847325762616927</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.9884128964918638</v>
       </c>
     </row>
     <row r="13">
@@ -1047,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>941</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>913</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1854</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.9831845533667184</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.984924016841806</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.9840083470105644</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>678968</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>611922</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>1290890</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.9742045800160193</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.9751010296607852</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.9780696166234746</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>672766; 683176</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>605820; 615501</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>1283099; 1297147</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.989278034787609</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.9906844352254121</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.9887781281127541</v>
       </c>
     </row>
     <row r="16">
@@ -1129,4 +781,376 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores vacunados de la triple vírica (tasa de respuesta: 98,91%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>78</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>67</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>54303</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>45874</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>100177</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>50720</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>43544</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>96698</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>55612</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>46399</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>101731</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>631</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>627</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>1258</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>458588</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>422992</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>881580</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>453600</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>419450</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>874907</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>462009</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>425158</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>885538</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>232</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>219</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>166077</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>143056</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>309133</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>163927</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>137916</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>303827</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>167293</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>145622</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>312090</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>941</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>913</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>1854</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>678968</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>611922</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>1290890</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>672766</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>605820</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>1283099</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>683176</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>615501</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>1297147</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>